--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_25.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_25.xlsx
@@ -1,33 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{F2D0C3D7-EF82-432C-8DEB-DF0B49B57C2E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75276FD5-1422-4590-ABDD-A81CD63CD8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="14" firstSheet="12" windowHeight="9972" windowWidth="17280" xWindow="2652" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="2100"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PayNowNoCFCorp" r:id="rId1" sheetId="1"/>
-    <sheet name="PayNowSCFCorp" r:id="rId2" sheetId="2"/>
-    <sheet name="PayNowDCFCorp" r:id="rId3" sheetId="3"/>
-    <sheet name="PayNowNoCFPC" r:id="rId4" sheetId="4"/>
-    <sheet name="PayNowNoCFPS" r:id="rId5" sheetId="5"/>
-    <sheet name="PayNowSCFPC" r:id="rId6" sheetId="6"/>
-    <sheet name="PayNowSCFPS" r:id="rId7" sheetId="7"/>
-    <sheet name="PayNowDCFPC" r:id="rId8" sheetId="8"/>
-    <sheet name="PayNowDCFPS" r:id="rId9" sheetId="9"/>
-    <sheet name="CCDeferredCorp" r:id="rId10" sheetId="10"/>
-    <sheet name="CCDeferredPC" r:id="rId11" sheetId="11"/>
-    <sheet name="CCDeferredPS" r:id="rId12" sheetId="12"/>
-    <sheet name="CMCAutopayCorp" r:id="rId13" sheetId="13"/>
-    <sheet name="CMCAutopayPC" r:id="rId14" sheetId="14"/>
-    <sheet name="CMCAutopayPS" r:id="rId15" sheetId="15"/>
+    <sheet name="PayNowNoCFCorp" sheetId="1" r:id="rId1"/>
+    <sheet name="PayNowSCFCorp" sheetId="2" r:id="rId2"/>
+    <sheet name="PayNowDCFCorp" sheetId="3" r:id="rId3"/>
+    <sheet name="PayNowNoCFPC" sheetId="4" r:id="rId4"/>
+    <sheet name="PayNowNoCFPS" sheetId="5" r:id="rId5"/>
+    <sheet name="PayNowSCFPC" sheetId="6" r:id="rId6"/>
+    <sheet name="PayNowSCFPS" sheetId="7" r:id="rId7"/>
+    <sheet name="PayNowDCFPC" sheetId="8" r:id="rId8"/>
+    <sheet name="PayNowDCFPS" sheetId="9" r:id="rId9"/>
+    <sheet name="CCDeferredCorp" sheetId="10" r:id="rId10"/>
+    <sheet name="CCDeferredPC" sheetId="11" r:id="rId11"/>
+    <sheet name="CCDeferredPS" sheetId="12" r:id="rId12"/>
+    <sheet name="CMCAutopayCorp" sheetId="13" r:id="rId13"/>
+    <sheet name="CMCAutopayPC" sheetId="14" r:id="rId14"/>
+    <sheet name="CMCAutopayPS" sheetId="15" r:id="rId15"/>
+    <sheet name="NoModifyAmountCorp" sheetId="16" r:id="rId16"/>
+    <sheet name="NoModifyAmountPC" sheetId="17" r:id="rId17"/>
+    <sheet name="NoModifyAmountPS" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="49">
   <si>
     <t>Result</t>
   </si>
@@ -164,10 +167,28 @@
     <t>36</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Wed Jun 17 21:01:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:51:41 IST 2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>6425</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:52:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:54:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:47:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:50:07 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -217,21 +238,21 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -248,10 +269,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -286,7 +307,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -321,7 +342,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -415,21 +436,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -446,7 +467,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -498,18 +519,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,10 +575,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="C2" s="2"/>
@@ -594,16 +615,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FDE61D8-7CF1-49D2-A996-64AFB712BF1E}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FDE61D8-7CF1-49D2-A996-64AFB712BF1E}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,11 +668,11 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>29</v>
       </c>
       <c r="C2" s="2"/>
@@ -690,19 +711,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AE6D8D-F34E-463E-A3D6-73A9B86AA787}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AE6D8D-F34E-463E-A3D6-73A9B86AA787}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,11 +767,11 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>27</v>
       </c>
       <c r="C2" s="2"/>
@@ -789,16 +810,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E2CFD7-9168-4C15-B5C2-6B422B67345F}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E2CFD7-9168-4C15-B5C2-6B422B67345F}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,11 +863,11 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>28</v>
       </c>
       <c r="C2" s="2"/>
@@ -885,16 +906,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD24E98-DACC-40C0-87FD-9271E31E1FFB}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD24E98-DACC-40C0-87FD-9271E31E1FFB}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,19 +994,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6567C6-A273-4444-8EA7-54C5D296CFBC}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6567C6-A273-4444-8EA7-54C5D296CFBC}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,11 +1051,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>42</v>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1070,19 +1091,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB56C604-DE27-434E-8DF4-BE8B1A719D57}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB56C604-DE27-434E-8DF4-BE8B1A719D57}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,16 +1182,295 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3F56878-4595-4F24-A0EF-A0AAA2547546}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1DBEE7D-E3A4-45EF-8848-743B227B6D57}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57945B9-54E7-4B50-92D7-FDB1259BD422}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7697D698-49F8-4A0B-BEA0-A6D495642D78}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7697D698-49F8-4A0B-BEA0-A6D495642D78}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1215,10 +1515,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C2" s="2"/>
@@ -1255,16 +1555,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7F2A10-9AB6-44A9-9EBA-350C7BBB17EA}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7F2A10-9AB6-44A9-9EBA-350C7BBB17EA}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1309,10 +1609,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="C2" s="2"/>
@@ -1349,19 +1649,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51FD00C-B98F-49D1-8CE4-D4F2C8A9710C}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51FD00C-B98F-49D1-8CE4-D4F2C8A9710C}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1406,10 +1706,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>33</v>
       </c>
       <c r="C2" s="2"/>
@@ -1446,19 +1746,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8775988C-20AE-44DC-BC58-33CCD16B3646}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8775988C-20AE-44DC-BC58-33CCD16B3646}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1503,10 +1803,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>36</v>
       </c>
       <c r="C2" s="2"/>
@@ -1543,16 +1843,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F173BAE-65B9-40F8-BB0D-6432D06F36FD}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F173BAE-65B9-40F8-BB0D-6432D06F36FD}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1597,10 +1897,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C2" s="2"/>
@@ -1637,16 +1937,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47BC98FB-1787-42B5-B276-FAAC8FBBA260}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47BC98FB-1787-42B5-B276-FAAC8FBBA260}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1691,10 +1991,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>37</v>
       </c>
       <c r="C2" s="2"/>
@@ -1731,16 +2031,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20787F2B-7A45-47F8-8166-6100EAA66ED9}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20787F2B-7A45-47F8-8166-6100EAA66ED9}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1785,10 +2085,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C2" s="2"/>
@@ -1825,16 +2125,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9AA5C79-B6B5-49AC-B3DC-C635F63E0B4F}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9AA5C79-B6B5-49AC-B3DC-C635F63E0B4F}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1879,10 +2179,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C2" s="2"/>
@@ -1919,6 +2219,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_25.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_25.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="93">
   <si>
     <t>Result</t>
   </si>
@@ -189,6 +189,138 @@
   </si>
   <si>
     <t>Thu Sep 03 21:50:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:03:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:06:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:08:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:21:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:22:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:24:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:26:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:27:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:29:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:30:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:32:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:33:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:39:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:42:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:43:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:45:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:46:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:47:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:49:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:53:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:54:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:55:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:57:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:59:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:00:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:04:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:15:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:17:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:19:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:23:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:25:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:27:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:29:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:31:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:34:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:36:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:39:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:42:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:43:24 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -579,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -673,7 +805,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -772,7 +904,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -868,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1240,7 +1372,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1335,7 +1467,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1519,7 +1651,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1613,7 +1745,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1710,7 +1842,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1807,7 +1939,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1901,7 +2033,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1995,7 +2127,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2089,7 +2221,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2183,7 +2315,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_25.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_25.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="100">
   <si>
     <t>Result</t>
   </si>
@@ -321,6 +321,27 @@
   </si>
   <si>
     <t>Tue Oct 20 14:43:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 02:23:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 02:51:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:05:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:33:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:35:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:36:40 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1393,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1467,7 +1488,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1651,7 +1672,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2033,7 +2054,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2127,7 +2148,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
